--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104570_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104570_W13.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5438</v>
+        <v>6.9935</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2275</v>
+        <v>6.5171</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3163</v>
+        <v>0.4764</v>
       </c>
       <c r="G2" t="n">
-        <v>8.5532</v>
+        <v>8.5289</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6091</v>
+        <v>2.5916</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9441</v>
+        <v>5.9373</v>
       </c>
       <c r="J2" t="n">
-        <v>9.0908</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2645</v>
+        <v>2.2333</v>
       </c>
       <c r="L2" t="n">
-        <v>6.8263</v>
+        <v>6.8067</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5375</v>
+        <v>-0.5111</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3289</v>
+        <v>-0.8525</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4608</v>
+        <v>-1.1084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1318</v>
+        <v>0.2559</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3249</v>
+        <v>3.6123</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2068</v>
+        <v>1.7109</v>
       </c>
       <c r="F3" t="n">
-        <v>2.118</v>
+        <v>1.9013</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0839</v>
+        <v>2.0916</v>
       </c>
       <c r="H3" t="n">
-        <v>1.772</v>
+        <v>1.7693</v>
       </c>
       <c r="I3" t="n">
-        <v>0.312</v>
+        <v>0.3222</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5629</v>
+        <v>2.5461</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7419</v>
+        <v>1.7269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4789</v>
+        <v>-0.4546</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5831</v>
+        <v>-0.1394</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3206</v>
+        <v>-0.1492</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2625</v>
+        <v>0.0097</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3482</v>
+        <v>0.5024</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3868</v>
+        <v>-0.6453</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0385</v>
+        <v>1.1478</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6466</v>
+        <v>0.427</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6089</v>
+        <v>0.0713</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9622000000000001</v>
+        <v>0.3557</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7365</v>
+        <v>1.3409</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5629</v>
+        <v>0.1724</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8264</v>
+        <v>1.1686</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0898</v>
+        <v>-0.9139</v>
       </c>
       <c r="N4" t="n">
-        <v>0.046</v>
+        <v>-0.1011</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1359</v>
+        <v>-0.8129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4333</v>
+        <v>-0.1522</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8771</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5562</v>
+        <v>0.4683</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2812</v>
+        <v>0.3699</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.886</v>
+        <v>1.6605</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1672</v>
+        <v>-1.2905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8958</v>
+        <v>1.6487</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2264</v>
+        <v>2.6079</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3306</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8711</v>
+        <v>1.7165</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6927</v>
+        <v>2.5511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1785</v>
+        <v>-0.8345</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0247</v>
+        <v>-0.0678</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5337</v>
+        <v>0.0568</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>-0.1246</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2686</v>
+        <v>0.4449</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3962</v>
+        <v>0.1716</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1276</v>
+        <v>0.2733</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0738</v>
+        <v>-0.1235</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9757</v>
+        <v>-1.2638</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9019</v>
+        <v>1.1403</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4244</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0619</v>
+        <v>1.2345</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3625</v>
+        <v>-0.3338</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3592</v>
+        <v>0.8527</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1732</v>
+        <v>0.6895</v>
       </c>
       <c r="L6" t="n">
-        <v>1.186</v>
+        <v>0.1632</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9348</v>
+        <v>0.0481</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1113</v>
+        <v>0.5451</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8236</v>
+        <v>-0.497</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.725</v>
+        <v>-0.6875</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9739</v>
+        <v>-0.7506</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2489</v>
+        <v>0.0631</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1946</v>
+        <v>-0.2585</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1322</v>
+        <v>-0.1487</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0624</v>
+        <v>-0.1099</v>
       </c>
       <c r="G7" t="n">
-        <v>0.322</v>
+        <v>0.3226</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0736</v>
+        <v>1.0687</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7516</v>
+        <v>-0.746</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2651</v>
+        <v>1.2526</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1531</v>
+        <v>1.1409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9431</v>
+        <v>-0.93</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0278</v>
+        <v>-0.0349</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6539</v>
+        <v>0.5925</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1251</v>
+        <v>-0.7701</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4866</v>
+        <v>-0.2729</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6385</v>
+        <v>-0.4971</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8804</v>
+        <v>-1.8875</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3001</v>
+        <v>0.3042</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1805</v>
+        <v>-2.1917</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9533</v>
+        <v>-0.972</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9272</v>
+        <v>-0.9155</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6303</v>
+        <v>-0.2696</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>-0.3904</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3114</v>
+        <v>-1.1272</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2578</v>
+        <v>-2.4109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9464</v>
+        <v>1.2837</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2101</v>
+        <v>-2.2214</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7169</v>
+        <v>-1.7284</v>
       </c>
       <c r="I9" t="n">
         <v>-0.4931</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2375</v>
+        <v>-2.2667</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4484</v>
+        <v>-1.4694</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7891</v>
+        <v>-0.7973</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0274</v>
+        <v>0.0452</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7138</v>
+        <v>-0.5203</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0212</v>
+        <v>-0.0955</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7349</v>
+        <v>-0.4248</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4948</v>
+        <v>-1.3533</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9375</v>
+        <v>1.3904</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4323</v>
+        <v>-2.7437</v>
       </c>
       <c r="G10" t="n">
         <v>0.7758</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6666</v>
+        <v>0.6718</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1092</v>
+        <v>0.104</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7507</v>
+        <v>1.7347</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9749</v>
+        <v>-0.9588</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1001</v>
+        <v>0.2287</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9739</v>
+        <v>-0.5021</v>
       </c>
       <c r="U10" t="n">
-        <v>1.074</v>
+        <v>0.7308</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6727</v>
+        <v>-5.227</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3758</v>
+        <v>-5.1682</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2969</v>
+        <v>-0.0588</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.989</v>
+        <v>-5.9947</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9134</v>
+        <v>-1.9128</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.0756</v>
+        <v>-4.0818</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.4996</v>
+        <v>-4.52</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.9962</v>
+        <v>-3.0096</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4894</v>
+        <v>-1.4747</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0032</v>
+        <v>-0.5495</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.625700000000003</v>
+        <v>2.618499999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6445</v>
+        <v>1.3691</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9811999999999999</v>
+        <v>1.2495</v>
       </c>
       <c r="G12" t="n">
-        <v>4.6222</v>
+        <v>4.591699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>6.688300000000001</v>
+        <v>6.6781</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.065799999999999</v>
+        <v>-2.086400000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>10.9459</v>
+        <v>10.7248</v>
       </c>
       <c r="K12" t="n">
-        <v>6.935300000000001</v>
+        <v>6.8272</v>
       </c>
       <c r="L12" t="n">
-        <v>4.0108</v>
+        <v>3.897900000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.323499999999999</v>
+        <v>-6.133100000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2469</v>
+        <v>-0.1490000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.0768</v>
+        <v>-5.9842</v>
       </c>
       <c r="P12" t="n">
-        <v>5.6707</v>
+        <v>5.6907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.9392</v>
+        <v>-7.967099999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>13.61</v>
+        <v>13.6579</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5255</v>
+        <v>-2.5323</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.672800000000001</v>
+        <v>-4.6719</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1473</v>
+        <v>2.1398</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.1417</v>
+        <v>-5.1317</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3105</v>
+        <v>3.2835</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.452199999999999</v>
+        <v>-8.4152</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.793</v>
+        <v>4.2018</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6499</v>
+        <v>3.8356</v>
       </c>
       <c r="F13" t="n">
-        <v>1.143</v>
+        <v>0.3662</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6584</v>
+        <v>-0.6551</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0663</v>
+        <v>-1.071</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4079</v>
+        <v>0.416</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2913</v>
+        <v>1.2626</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1914</v>
+        <v>1.1839</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9497</v>
+        <v>-1.9177</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8519</v>
+        <v>1.2729</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8933</v>
+        <v>0.1272</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9586</v>
+        <v>1.1457</v>
       </c>
       <c r="V13" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7244</v>
+        <v>1.2037</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4921</v>
+        <v>1.8076</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7677</v>
+        <v>-0.604</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2519</v>
+        <v>1.2524</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7259</v>
+        <v>-0.7212</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7857</v>
+        <v>2.7556</v>
       </c>
       <c r="K14" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5338</v>
+        <v>-1.5032</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7543</v>
+        <v>-0.2764</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2521</v>
+        <v>-0.8993</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4978</v>
+        <v>0.6229</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1765</v>
+        <v>0.4914</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.061</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2375</v>
+        <v>1.1029</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4412</v>
+        <v>0.4413</v>
       </c>
       <c r="H15" t="n">
-        <v>1.049</v>
+        <v>1.0538</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6078</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6297</v>
+        <v>0.6105</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1885</v>
+        <v>-0.1692</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4158</v>
+        <v>0.733</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.8168</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0218</v>
+        <v>-0.1189</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8487</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2034</v>
+        <v>-1.45</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2568</v>
+        <v>-0.8041</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0533</v>
+        <v>-0.6459</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2445</v>
+        <v>0.0231</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6896</v>
+        <v>-0.2003</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4451</v>
+        <v>0.2234</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.959</v>
+        <v>-1.4731</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5672</v>
+        <v>-0.6037</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>-0.8694</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0909</v>
+        <v>0.3995</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5081</v>
+        <v>0.0019</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5828</v>
+        <v>0.3975</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7712</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1762,13 +1762,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5619</v>
+        <v>-0.5951</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1229</v>
+        <v>-1.2437</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4389</v>
+        <v>0.6486</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4605</v>
+        <v>-1.2054</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8023</v>
+        <v>-1.2606</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6583</v>
+        <v>0.0552</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0365</v>
+        <v>-0.261</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1874</v>
+        <v>-0.7002</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2239</v>
+        <v>0.4392</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4971</v>
+        <v>-0.9444</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6149</v>
+        <v>-0.5604</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8822</v>
+        <v>-0.384</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0333</v>
+        <v>0.5192</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1179</v>
+        <v>0.1555</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0847</v>
+        <v>0.3637</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.7739</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5628</v>
+        <v>-0.6582</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1897</v>
+        <v>0.6943</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7525</v>
+        <v>-1.3525</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4964</v>
+        <v>1.5013</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7446</v>
+        <v>0.7412</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7517</v>
+        <v>0.7601</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8421</v>
+        <v>1.8284</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3458</v>
+        <v>-0.3271</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0611</v>
+        <v>-0.1579</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1603</v>
+        <v>-0.3115</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2214</v>
+        <v>0.1535</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4264</v>
+        <v>-0.853</v>
       </c>
       <c r="E20" t="n">
-        <v>0.143</v>
+        <v>-0.388</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5694</v>
+        <v>-0.465</v>
       </c>
       <c r="G20" t="n">
-        <v>0.388</v>
+        <v>-1.2272</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2726</v>
+        <v>-2.9298</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6607</v>
+        <v>1.7026</v>
       </c>
       <c r="J20" t="n">
-        <v>1.736</v>
+        <v>1.0179</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6896</v>
+        <v>-1.938</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4256</v>
+        <v>2.9559</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.348</v>
+        <v>-2.2451</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5831</v>
+        <v>-0.9918</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7649</v>
+        <v>-1.2533</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5441</v>
+        <v>-0.2404</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>-0.4255</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1267</v>
+        <v>0.1851</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7712</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3214</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1542</v>
+        <v>-1.0309</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1745</v>
+        <v>0.2336</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9798</v>
+        <v>-1.2645</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2318</v>
+        <v>0.389</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9351</v>
+        <v>-1.2751</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7033</v>
+        <v>1.6641</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0511</v>
+        <v>1.7202</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9262</v>
+        <v>-0.7002</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9772</v>
+        <v>2.4204</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2829</v>
+        <v>-1.3312</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0089</v>
+        <v>-0.5749</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.274</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5349</v>
+        <v>-0.1451</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2521</v>
+        <v>-0.2998</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2828</v>
+        <v>0.1546</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3856</v>
+        <v>0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2249</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2196</v>
+        <v>-4.8869</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.2273</v>
+        <v>-5.5538</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0077</v>
+        <v>0.667</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2725</v>
+        <v>-3.2657</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.423</v>
+        <v>-0.4113</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8495</v>
+        <v>-2.8543</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.8045</v>
+        <v>-2.8243</v>
       </c>
       <c r="K22" t="n">
-        <v>0.381</v>
+        <v>0.3792</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1855</v>
+        <v>-3.2035</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.468</v>
+        <v>-0.4414</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O22" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0944</v>
+        <v>0.4275</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.113</v>
+        <v>-0.4046</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2073</v>
+        <v>0.832</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.625999999999999</v>
+        <v>-2.6185</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9815000000000005</v>
+        <v>-1.2494</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6446</v>
+        <v>-1.3689</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.6223</v>
+        <v>-4.5918</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.6884</v>
+        <v>-6.6781</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0659</v>
+        <v>2.086599999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>6.3234</v>
+        <v>6.133</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2467000000000001</v>
+        <v>0.1489999999999997</v>
       </c>
       <c r="L23" t="n">
-        <v>6.0765</v>
+        <v>5.9841</v>
       </c>
       <c r="M23" t="n">
-        <v>-10.946</v>
+        <v>-10.7248</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.935199999999999</v>
+        <v>-6.8271</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.0107</v>
+        <v>-3.8978</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.6709</v>
+        <v>-5.6909</v>
       </c>
       <c r="Q23" t="n">
-        <v>-13.6102</v>
+        <v>-13.6582</v>
       </c>
       <c r="R23" t="n">
-        <v>7.939299999999999</v>
+        <v>7.9673</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5253</v>
+        <v>2.5323</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.1473</v>
+        <v>-2.1399</v>
       </c>
       <c r="U23" t="n">
-        <v>4.6726</v>
+        <v>4.6718</v>
       </c>
       <c r="V23" t="n">
-        <v>5.141800000000001</v>
+        <v>5.1318</v>
       </c>
       <c r="W23" t="n">
-        <v>8.452300000000001</v>
+        <v>8.4153</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.3104</v>
+        <v>-3.283399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104570_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104570_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.4152</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104570_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-3.283399999999999</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
